--- a/stories/arbres/ATOM-VIV.ANI.003-08.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hélène est près du clapier. Le lapin a les oreilles douces. Maman, l'adulte, tient la bouteille. Hélène verse l'eau. Elle est douce. Sa main va lentement. Parce qu'elle est avec un adulte, le lapin boit. Hélène dit : doux. Avec un adulte. L'eau cloche dans le bol. Maman sourit. Hélène reste près de maman. Le lapin croque une feuille.</t>
+          <t>Hélène est près du clapier. Le lapin a les oreilles douces. Maman, l'adulte, tient la bouteille. Hélène verse l'eau. Elle est douce. Sa main va lentement. Parce qu'elle est avec un adulte, le lapin boit. Doux. Avec un adulte. L'eau cloche dans le bol. Maman sourit. Hélène reste près de maman. Le lapin croque une feuille.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hélène est près du clapier. Le lapin a les oreilles douces. Maman, l'adulte, tient la bouteille. Hélène verse l'eau. Elle est douce. Sa main va lentement. Parce qu'elle est avec un adulte, le lapin boit.
+enfant-f|Doux. Avec un adulte. L'eau cloche dans le bol. Maman sourit.
+narrateur|Hélène reste près de maman. Le lapin croque une feuille.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hélène donne l'eau au lapin. Comment, et avec qui ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hélène a versé l'eau avec un adulte. Elle a été douce. Maman était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hélène referme le clapier avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.003-08.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Hélène reste près de maman. Le lapin croque une feuille.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Hélène donne l'eau au lapin. Comment, et avec qui ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Hélène a versé l'eau avec un adulte. Elle a été douce. Maman était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1849,7 @@
           <t>narrateur|Hélène referme le clapier avec maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.003-08.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hélène prend soin du lapin avec maman</t>
+          <t>La feuille du clapier</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah veut donner une feuille fraîche au lapin. La paille sent le foin. La bouteille est trop pleine. Avec maman, elle verse tout doux. Le lapin boit, puis croque.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hélène est près du clapier. Le lapin a les oreilles douces. Maman, l'adulte, tient la bouteille. Hélène verse l'eau. Elle est douce. Sa main va lentement. Parce qu'elle est avec un adulte, le lapin boit. Doux. Avec un adulte. L'eau cloche dans le bol. Maman sourit. Hélène reste près de maman. Le lapin croque une feuille.</t>
+          <t>La paille du clapier sent le foin chaud. Un carré de soleil pose sur le loquet. Dehors, une abeille passe près du bois. Le jardin sent l'herbe coupée. Sarah vit ici, avec maman. Tu as vu la petite fenêtre ? Elle est ouverte, un peu. En ce moment, Sarah s'approche du clapier. Le bois est rêche sous ses doigts. Une oreille rose bouge derrière la paille. Il est là. Je veux lui donner une feuille. Une feuille bien verte ? Oui. Et de l'eau, aussi. Le bol de terre est presque vide. Une croûte sèche au fond. Le lapin a le nez poudreux. Il a soif, je crois. On va être tout doux ? Tout doux. Maman tient la bouteille d'eau. Sarah pose la main sur le plastique. Elle est lourde. Oui. On verse ensemble, tout lentement. Sarah penche un peu trop. Une goutte saute sur la paille. Oh. Doucement. La paille n'aime pas le bain. Le lapin recule sous le foin. On ne voit plus que le bout du nez. Il a peur ? Il attend. On reste près de lui ? Oui, maman. Sarah respire. Sa main redevient lente. L'eau glisse, un fil très mince. Le bol se remplit sans éclabousser. Ça fait un tout petit cloc. Cloc. Voilà. Avec maman, tout doux. Le nez poudreux avance. Les moustaches tremblent. Le lapin boit, par petites gorgées. Il boit ! Tu as versé avec un adulte. Merci, Sarah.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hélène est près du clapier. Le lapin a les oreilles douces. Maman, l'adulte, tient la bouteille. Hélène verse l'eau. Elle est douce. Sa main va lentement. Parce qu'elle est &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; un adulte, le lapin boit. Hélène dit : doux. Avec un adulte. L'eau cloche dans le bol. Maman sourit. Hélène reste près de maman. Le lapin croque une feuille.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La paille du clapier sent le foin chaud. Un carré de soleil pose sur le loquet. Dehors, une abeille passe près du bois. Le jardin sent l'herbe coupée. Sarah vit ici, avec maman. Tu as vu la petite fenêtre ? Elle est ouverte, un peu. En ce moment, Sarah s'approche du clapier. Le bois est rêche sous ses doigts. Une oreille rose bouge derrière la paille. Il est là. Je veux lui donner une feuille. Une feuille bien verte ? Oui. Et de l'eau, aussi. Le bol de terre est presque vide. Une croûte sèche au fond. Le lapin a le nez poudreux. Il a soif, je crois. On va être tout doux ? Tout doux. Maman tient la bouteille d'eau. Sarah pose la main sur le plastique. Elle est lourde. Oui. On verse ensemble, tout lentement. Sarah penche un peu trop. Une goutte saute sur la paille. Oh. Doucement. La paille n'aime pas le bain. Le lapin recule sous le foin. On ne voit plus que le bout du nez. Il a peur ? Il attend. On reste près de lui ? Oui, maman. Sarah respire. Sa main redevient lente. L'eau glisse, un fil très mince. Le bol se remplit sans éclabousser. Ça fait un tout petit cloc. Cloc. Voilà. Avec maman, tout doux. Le nez poudreux avance. Les moustaches tremblent. Le lapin boit, par petites gorgées. Il boit ! Tu as versé avec un adulte. Merci, Sarah.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,9 +1324,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hélène est près du clapier. Le lapin a les oreilles douces. Maman, l'adulte, tient la bouteille. Hélène verse l'eau. Elle est douce. Sa main va lentement. Parce qu'elle est avec un adulte, le lapin boit.
-enfant-f|Doux. Avec un adulte. L'eau cloche dans le bol. Maman sourit.
-narrateur|Hélène reste près de maman. Le lapin croque une feuille.</t>
+          <t>narrateur|La paille du clapier sent le foin chaud.
+narrateur|Un carré de soleil pose sur le loquet.
+narrateur|Dehors, une abeille passe près du bois.
+narrateur|Le jardin sent l'herbe coupée.
+narrateur|Sarah vit ici, avec maman.
+maman|Tu as vu la petite fenêtre ?
+enfant-f|Elle est ouverte, un peu.
+narrateur|En ce moment, Sarah s'approche du clapier.
+narrateur|Le bois est rêche sous ses doigts.
+narrateur|Une oreille rose bouge derrière la paille.
+enfant-f|Il est là.
+enfant-f|Je veux lui donner une feuille.
+maman|Une feuille bien verte ?
+enfant-f|Oui.
+enfant-f|Et de l'eau, aussi.
+narrateur|Le bol de terre est presque vide.
+narrateur|Une croûte sèche au fond.
+narrateur|Le lapin a le nez poudreux.
+maman|Il a soif, je crois.
+maman|On va être tout doux ?
+enfant-f|Tout doux.
+narrateur|Maman tient la bouteille d'eau.
+narrateur|Sarah pose la main sur le plastique.
+enfant-f|Elle est lourde.
+maman|Oui.
+maman|On verse ensemble, tout lentement.
+narrateur|Sarah penche un peu trop.
+narrateur|Une goutte saute sur la paille.
+enfant-f|Oh.
+maman|Doucement.
+maman|La paille n'aime pas le bain.
+narrateur|Le lapin recule sous le foin.
+narrateur|On ne voit plus que le bout du nez.
+enfant-f|Il a peur ?
+maman|Il attend.
+maman|On reste près de lui ?
+enfant-f|Oui, maman.
+narrateur|Sarah respire.
+narrateur|Sa main redevient lente.
+narrateur|L'eau glisse, un fil très mince.
+narrateur|Le bol se remplit sans éclabousser.
+narrateur|Ça fait un tout petit cloc.
+enfant-f|Cloc.
+maman|Voilà.
+maman|Avec maman, tout doux.
+narrateur|Le nez poudreux avance.
+narrateur|Les moustaches tremblent.
+narrateur|Le lapin boit, par petites gorgées.
+enfant-f|Il boit !
+maman|Tu as versé avec un adulte.
+maman|Merci, Sarah.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1346,12 +1406,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hélène donne l'eau au lapin. Comment, et avec qui ?</t>
+          <t>Sarah donne l'eau au lapin. Comment, et avec qui ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hélène donne l'eau au lapin. Comment, et &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; qui ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah donne l'eau au lapin. Comment, et avec qui ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1381,7 +1441,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>On est doux. On est avec un adulte. Que fait Hélène ?</t>
+          <t>On est doux. On est avec un adulte. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1430,7 +1490,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1566,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hélène donne l'eau au lapin. Comment, et avec qui ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah donne l'eau au lapin.
+narrateur|Comment, et avec qui ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1534,12 +1594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hélène a versé l'eau avec un adulte. Elle a été douce. Maman était là.</t>
+          <t>Sarah a versé tout doux, avec maman. Le bol est plein, pas trop. La paille reste sèche autour. Il a encore soif ? Il boit à sa vitesse. On le regarde, on ne le presse pas. Sarah glisse la feuille verte. Elle passe entre les barreaux. Le bois sent encore le foin. Prends, petit. Le lapin croque. Ça fait un bruit de salade. Tu entends ? Croc, croc. Tu as été douce. On referme le loquet ensemble ? Oui. Sarah pousse le loquet. Il fait un petit clic de bois. Clic. Une paille reste collée à sa paume. Elle la garde, tout contre le pouce.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hélène a versé l'eau &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; un adulte. Elle a été douce. Maman était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a versé tout doux, avec maman. Le bol est plein, pas trop. La paille reste sèche autour. Il a encore soif ? Il boit à sa vitesse. On le regarde, on ne le presse pas. Sarah glisse la feuille verte. Elle passe entre les barreaux. Le bois sent encore le foin. Prends, petit. Le lapin croque. Ça fait un bruit de salade. Tu entends ? Croc, croc. Tu as été douce. On referme le loquet ensemble ? Oui. Sarah pousse le loquet. Il fait un petit clic de bois. Clic. Une paille reste collée à sa paume. Elle la garde, tout contre le pouce.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1602,7 +1662,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1678,10 +1738,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hélène a versé l'eau avec un adulte. Elle a été douce. Maman était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah a versé tout doux, avec maman.
+narrateur|Le bol est plein, pas trop.
+narrateur|La paille reste sèche autour.
+enfant-f|Il a encore soif ?
+maman|Il boit à sa vitesse.
+maman|On le regarde, on ne le presse pas.
+narrateur|Sarah glisse la feuille verte.
+narrateur|Elle passe entre les barreaux.
+narrateur|Le bois sent encore le foin.
+enfant-f|Prends, petit.
+narrateur|Le lapin croque.
+narrateur|Ça fait un bruit de salade.
+maman|Tu entends ?
+enfant-f|Croc, croc.
+maman|Tu as été douce.
+maman|On referme le loquet ensemble ?
+enfant-f|Oui.
+narrateur|Sarah pousse le loquet.
+narrateur|Il fait un petit clic de bois.
+maman|Clic.
+narrateur|Une paille reste collée à sa paume.
+narrateur|Elle la garde, tout contre le pouce.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1706,12 +1786,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hélène referme le clapier avec maman.</t>
+          <t>Le soleil a glissé sur le toit du clapier. L'ombre est plus longue, plus douce. Il a fini sa feuille. Il en a encore une, près du bol. Sarah se baisse. Le jardin sent l'herbe et le foin. Tu veux rester un peu ? Un peu. Le lapin se lèche la patte. Ses oreilles retombent, calmes. Il est bien. Oui. Parce qu'on a été doux. Sarah pose le front au bois. Le bois est tiède. Dedans, on entend un tout petit souffle. Tu lui diras bonsoir ? Bonsoir, lapin. Une abeille passe encore, plus loin. Le loquet tient.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hélène referme le clapier &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le soleil a glissé sur le toit du clapier. L'ombre est plus longue, plus douce. Il a fini sa feuille. Il en a encore une, près du bol. Sarah se baisse. Le jardin sent l'herbe et le foin. Tu veux rester un peu ? Un peu. Le lapin se lèche la patte. Ses oreilles retombent, calmes. Il est bien. Oui. Parce qu'on a été doux. Sarah pose le front au bois. Le bois est tiède. Dedans, on entend un tout petit souffle. Tu lui diras bonsoir ? Bonsoir, lapin. Une abeille passe encore, plus loin. Le loquet tient.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1774,7 +1854,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1846,10 +1926,28 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hélène referme le clapier avec maman.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le soleil a glissé sur le toit du clapier.
+narrateur|L'ombre est plus longue, plus douce.
+enfant-f|Il a fini sa feuille.
+maman|Il en a encore une, près du bol.
+narrateur|Sarah se baisse.
+narrateur|Le jardin sent l'herbe et le foin.
+maman|Tu veux rester un peu ?
+enfant-f|Un peu.
+narrateur|Le lapin se lèche la patte.
+narrateur|Ses oreilles retombent, calmes.
+enfant-f|Il est bien.
+maman|Oui.
+maman|Parce qu'on a été doux.
+narrateur|Sarah pose le front au bois.
+narrateur|Le bois est tiède.
+narrateur|Dedans, on entend un tout petit souffle.
+maman|Tu lui diras bonsoir ?
+enfant-f|Bonsoir, lapin.
+narrateur|Une abeille passe encore, plus loin.
+narrateur|Le loquet tient.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1874,12 +1972,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah ouvre la main. Le brin de paille sent encore le foin. Il a bu. Il a croqué. Oui. Avec toi, tout doux. Le foin tiède reste dans sa main.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah ouvre la main. Le brin de paille sent encore le foin. Il a bu. Il a croqué. Oui. Avec toi, tout doux. Le foin tiède reste dans sa main.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1935,14 +2033,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2014,10 +2112,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Sarah ouvre la main.
+narrateur|Le brin de paille sent encore le foin.
+enfant-f|Il a bu.
+enfant-f|Il a croqué.
+maman|Oui.
+maman|Avec toi, tout doux.
+narrateur|Le foin tiède reste dans sa main.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2036,7 +2139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2177,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.003-08.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-08.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin, clapier</t>
+          <t>jardin, clapier à la fenêtre de paille</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hélène, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>
